--- a/AAII_Financials/Quarterly/CGXYY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CGXYY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="92">
   <si>
     <t>CGXYY</t>
   </si>
@@ -656,68 +656,77 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -754,8 +763,17 @@
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -792,8 +810,17 @@
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -830,8 +857,17 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -846,8 +882,11 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -884,8 +923,17 @@
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -922,8 +970,17 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -960,8 +1017,17 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -998,8 +1064,17 @@
       <c r="N15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1011,8 +1086,11 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1049,8 +1127,17 @@
       <c r="N17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1087,8 +1174,17 @@
       <c r="N18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1103,8 +1199,11 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1141,8 +1240,17 @@
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1179,8 +1287,17 @@
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1217,8 +1334,17 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1255,8 +1381,17 @@
       <c r="N23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1293,8 +1428,17 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1331,8 +1475,17 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1369,8 +1522,17 @@
       <c r="N26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1407,8 +1569,17 @@
       <c r="N27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1445,8 +1616,17 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1483,8 +1663,17 @@
       <c r="N29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1521,8 +1710,17 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1559,8 +1757,17 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1597,8 +1804,17 @@
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1635,8 +1851,17 @@
       <c r="N33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1673,8 +1898,17 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1711,51 +1945,69 @@
       <c r="N35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1770,8 +2022,11 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1786,122 +2041,152 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3052800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3339000</v>
+      </c>
+      <c r="F41" s="3">
+        <v>2618900</v>
+      </c>
+      <c r="G41" s="3">
         <v>2746500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="H41" s="3">
         <v>2319700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="I41" s="3">
         <v>2356300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="J41" s="3">
         <v>2231600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="K41" s="3">
         <v>2215600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="L41" s="3">
         <v>2361300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="M41" s="3">
         <v>2210000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="N41" s="3">
         <v>2696000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="O41" s="3">
         <v>2355000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="P41" s="3">
         <v>2890800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="Q41" s="3">
         <v>2438600</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>73189300</v>
+      </c>
+      <c r="E42" s="3">
+        <v>68885400</v>
+      </c>
+      <c r="F42" s="3">
+        <v>57568200</v>
+      </c>
+      <c r="G42" s="3">
         <v>61856600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="H42" s="3">
         <v>55873300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="I42" s="3">
         <v>52400900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="J42" s="3">
         <v>44044500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="K42" s="3">
         <v>58994000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="L42" s="3">
         <v>55533500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="M42" s="3">
         <v>56790900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="N42" s="3">
         <v>42942500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="O42" s="3">
         <v>45884400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="P42" s="3">
         <v>42200500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="Q42" s="3">
         <v>45489000</v>
       </c>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>27345500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>24084400</v>
+      </c>
+      <c r="F43" s="3">
+        <v>22056700</v>
+      </c>
+      <c r="G43" s="3">
         <v>20499700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="H43" s="3">
         <v>15955500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="I43" s="3">
         <v>16144100</v>
       </c>
-      <c r="G43" s="3">
-        <v>15481100</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
+        <v>15480000</v>
+      </c>
+      <c r="K43" s="3">
         <v>14216000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="L43" s="3">
         <v>13531800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="M43" s="3">
         <v>13690700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="N43" s="3">
         <v>14764900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="O43" s="3">
         <v>13465300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="P43" s="3">
         <v>13803100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="Q43" s="3">
         <v>14443200</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1914,222 +2199,276 @@
       <c r="F44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G44" s="3">
-        <v>162500</v>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L44" s="3">
         <v>354700</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N44" s="3">
         <v>304600</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P44" s="3">
         <v>301100</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>24120100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>20203200</v>
+      </c>
+      <c r="F45" s="3">
+        <v>13046400</v>
+      </c>
+      <c r="G45" s="3">
         <v>11849800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="H45" s="3">
         <v>9777000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="I45" s="3">
         <v>8479700</v>
       </c>
-      <c r="G45" s="3">
-        <v>8179800</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
+        <v>8343400</v>
+      </c>
+      <c r="K45" s="3">
         <v>8447900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="L45" s="3">
         <v>7552000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="M45" s="3">
         <v>7034100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="N45" s="3">
         <v>7501000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="O45" s="3">
         <v>8315400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="P45" s="3">
         <v>8446700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="Q45" s="3">
         <v>7500800</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>127707700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>116512100</v>
+      </c>
+      <c r="F46" s="3">
+        <v>95290200</v>
+      </c>
+      <c r="G46" s="3">
         <v>96952600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="H46" s="3">
         <v>83925400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="I46" s="3">
         <v>79381000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="J46" s="3">
         <v>70099500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="K46" s="3">
         <v>83873400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="L46" s="3">
         <v>79333300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="M46" s="3">
         <v>79725700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="N46" s="3">
         <v>68209000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="O46" s="3">
         <v>70020100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="P46" s="3">
         <v>67642100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="Q46" s="3">
         <v>69871600</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>27210300</v>
+      </c>
+      <c r="E47" s="3">
+        <v>23807200</v>
+      </c>
+      <c r="F47" s="3">
+        <v>26121000</v>
+      </c>
+      <c r="G47" s="3">
         <v>22573000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="H47" s="3">
         <v>24292000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="I47" s="3">
         <v>22322900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="J47" s="3">
         <v>29982900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="K47" s="3">
         <v>20962200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="L47" s="3">
         <v>25211900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="M47" s="3">
         <v>24802000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="N47" s="3">
         <v>24315500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="O47" s="3">
         <v>20942600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="P47" s="3">
         <v>26679700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="Q47" s="3">
         <v>23770700</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>352500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>325100</v>
+      </c>
+      <c r="F48" s="3">
+        <v>316800</v>
+      </c>
+      <c r="G48" s="3">
         <v>228800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="H48" s="3">
         <v>265800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="I48" s="3">
         <v>267500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="J48" s="3">
         <v>305600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="K48" s="3">
         <v>269500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="L48" s="3">
         <v>283300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="M48" s="3">
         <v>288500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="N48" s="3">
         <v>328000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="O48" s="3">
         <v>302100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="P48" s="3">
         <v>312200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="Q48" s="3">
         <v>319700</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>267900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>269800</v>
+      </c>
+      <c r="F49" s="3">
+        <v>277300</v>
+      </c>
+      <c r="G49" s="3">
         <v>263600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="H49" s="3">
         <v>265600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="I49" s="3">
         <v>259100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="J49" s="3">
         <v>262400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="K49" s="3">
         <v>267800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="L49" s="3">
         <v>250100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="M49" s="3">
         <v>252800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="N49" s="3">
         <v>261400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="O49" s="3">
         <v>241900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="P49" s="3">
         <v>247200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="Q49" s="3">
         <v>257900</v>
       </c>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2166,8 +2505,17 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2204,46 +2552,64 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>534200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1256800</v>
+      </c>
+      <c r="F52" s="3">
+        <v>301100</v>
+      </c>
+      <c r="G52" s="3">
         <v>894200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="H52" s="3">
         <v>330900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="I52" s="3">
         <v>1084000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="J52" s="3">
         <v>346000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="K52" s="3">
         <v>1222400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="L52" s="3">
         <v>343400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="M52" s="3">
         <v>1378000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="N52" s="3">
         <v>376200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="O52" s="3">
         <v>1150900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="P52" s="3">
         <v>301200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="Q52" s="3">
         <v>1256500</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2280,46 +2646,64 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>156117400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>142212800</v>
+      </c>
+      <c r="F54" s="3">
+        <v>122347200</v>
+      </c>
+      <c r="G54" s="3">
         <v>120953600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="H54" s="3">
         <v>109123700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="I54" s="3">
         <v>103352900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="J54" s="3">
         <v>101035800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="K54" s="3">
         <v>106624600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="L54" s="3">
         <v>105452000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="M54" s="3">
         <v>106481600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="N54" s="3">
         <v>93529100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="O54" s="3">
         <v>92690100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="P54" s="3">
         <v>95209900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="Q54" s="3">
         <v>95509400</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2334,8 +2718,11 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2350,236 +2737,293 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>51897600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>45891100</v>
+      </c>
+      <c r="F57" s="3">
+        <v>31892900</v>
+      </c>
+      <c r="G57" s="3">
         <v>32459900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="H57" s="3">
         <v>27822900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="I57" s="3">
         <v>24596600</v>
       </c>
-      <c r="G57" s="3">
-        <v>23695900</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
+        <v>22732600</v>
+      </c>
+      <c r="K57" s="3">
         <v>26301200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="L57" s="3">
         <v>25210400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="M57" s="3">
         <v>25067100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="N57" s="3">
         <v>18220400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="O57" s="3">
         <v>16276500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="P57" s="3">
         <v>16923600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="Q57" s="3">
         <v>19241200</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>10132800</v>
+        <v>50283400</v>
       </c>
       <c r="E58" s="3">
+        <v>37720000</v>
+      </c>
+      <c r="F58" s="3">
+        <v>44491800</v>
+      </c>
+      <c r="G58" s="3">
+        <v>36110600</v>
+      </c>
+      <c r="H58" s="3">
         <v>37662500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="I58" s="3">
         <v>32719500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="J58" s="3">
         <v>37607100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="K58" s="3">
         <v>29392500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="L58" s="3">
         <v>37361100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="M58" s="3">
         <v>32910500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="N58" s="3">
         <v>36236500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="O58" s="3">
         <v>29280200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="P58" s="3">
         <v>38178100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="Q58" s="3">
         <v>31159100</v>
       </c>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>14577400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>10528500</v>
+      </c>
+      <c r="F59" s="3">
+        <v>11147200</v>
+      </c>
+      <c r="G59" s="3">
         <v>9240500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="H59" s="3">
         <v>10372800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="I59" s="3">
         <v>6841900</v>
       </c>
-      <c r="G59" s="3">
-        <v>8329600</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
+        <v>9292900</v>
+      </c>
+      <c r="K59" s="3">
         <v>8560500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="L59" s="3">
         <v>13111700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="M59" s="3">
         <v>14332500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="N59" s="3">
         <v>8872700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="O59" s="3">
         <v>7566700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="P59" s="3">
         <v>11000500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="Q59" s="3">
         <v>7431700</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>53125600</v>
+        <v>118059900</v>
       </c>
       <c r="E60" s="3">
+        <v>95233400</v>
+      </c>
+      <c r="F60" s="3">
+        <v>88622300</v>
+      </c>
+      <c r="G60" s="3">
+        <v>79103400</v>
+      </c>
+      <c r="H60" s="3">
         <v>77278100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="I60" s="3">
         <v>65153800</v>
       </c>
-      <c r="G60" s="3">
-        <v>70702700</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
+        <v>70428200</v>
+      </c>
+      <c r="K60" s="3">
         <v>65169600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="L60" s="3">
         <v>76694100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="M60" s="3">
         <v>73031400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="N60" s="3">
         <v>64320800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="O60" s="3">
         <v>53884000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="P60" s="3">
         <v>67103900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="Q60" s="3">
         <v>58587500</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>41562200</v>
+        <v>14775600</v>
       </c>
       <c r="E61" s="3">
+        <v>19108000</v>
+      </c>
+      <c r="F61" s="3">
+        <v>12122400</v>
+      </c>
+      <c r="G61" s="3">
+        <v>15584400</v>
+      </c>
+      <c r="H61" s="3">
         <v>11382000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="I61" s="3">
         <v>13925700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="J61" s="3">
         <v>10797200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="K61" s="3">
         <v>15418000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="L61" s="3">
         <v>10142300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="M61" s="3">
         <v>14939200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="N61" s="3">
         <v>10750300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="O61" s="3">
         <v>15839600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="P61" s="3">
         <v>10101800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="Q61" s="3">
         <v>17033300</v>
       </c>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>172300</v>
+      </c>
+      <c r="E62" s="3">
+        <v>5026000</v>
+      </c>
+      <c r="F62" s="3">
+        <v>255900</v>
+      </c>
+      <c r="G62" s="3">
         <v>4568400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="H62" s="3">
         <v>13800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="I62" s="3">
         <v>4403100</v>
       </c>
-      <c r="G62" s="3">
-        <v>10500</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
+        <v>231000</v>
+      </c>
+      <c r="K62" s="3">
         <v>6372300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="L62" s="3">
         <v>27100</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N62" s="3">
         <v>25300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="O62" s="3">
         <v>6381400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="P62" s="3">
         <v>1575200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="Q62" s="3">
         <v>4409000</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2616,8 +3060,17 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2654,8 +3107,17 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2692,46 +3154,64 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>133193200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>119576600</v>
+      </c>
+      <c r="F66" s="3">
+        <v>101216500</v>
+      </c>
+      <c r="G66" s="3">
         <v>99545300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="H66" s="3">
         <v>89001100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="I66" s="3">
         <v>83751800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="J66" s="3">
         <v>81787000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="K66" s="3">
         <v>87136800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="L66" s="3">
         <v>87017600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="M66" s="3">
         <v>88057100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="N66" s="3">
         <v>75125900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="O66" s="3">
         <v>76162400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="P66" s="3">
         <v>78995500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="Q66" s="3">
         <v>80137400</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2746,8 +3226,11 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2784,8 +3267,17 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2822,8 +3314,17 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2860,8 +3361,17 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2898,46 +3408,64 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>10971700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>10617800</v>
+      </c>
+      <c r="F72" s="3">
+        <v>9991800</v>
+      </c>
+      <c r="G72" s="3">
         <v>9821800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="H72" s="3">
         <v>9112100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="I72" s="3">
         <v>8921900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="J72" s="3">
         <v>8438300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="K72" s="3">
         <v>8539900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="L72" s="3">
         <v>7849300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="M72" s="3">
         <v>8011700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="N72" s="3">
         <v>7925500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="O72" s="3">
         <v>7527100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="P72" s="3">
         <v>7338100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="Q72" s="3">
         <v>7820100</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2974,8 +3502,17 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3012,8 +3549,17 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3050,46 +3596,64 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>22921800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>22633800</v>
+      </c>
+      <c r="F76" s="3">
+        <v>21128400</v>
+      </c>
+      <c r="G76" s="3">
         <v>21405900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="H76" s="3">
         <v>20120000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="I76" s="3">
         <v>19598500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="J76" s="3">
         <v>19246300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="K76" s="3">
         <v>19483700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="L76" s="3">
         <v>18430500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="M76" s="3">
         <v>18420500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="N76" s="3">
         <v>18399100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="O76" s="3">
         <v>16524600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="P76" s="3">
         <v>16211100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="Q76" s="3">
         <v>15368700</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3126,51 +3690,69 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3207,8 +3789,17 @@
       <c r="N81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3223,46 +3814,58 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>64900</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3">
+        <v>122300</v>
+      </c>
+      <c r="G83" s="3">
         <v>-64300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="H83" s="3">
         <v>62000</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3">
         <v>124400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="K83" s="3">
         <v>-58800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="L83" s="3">
         <v>59100</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N83" s="3">
         <v>116900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="O83" s="3">
         <v>-53700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="P83" s="3">
         <v>57100</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3299,8 +3902,17 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3337,8 +3949,17 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3375,8 +3996,17 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3413,8 +4043,17 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3451,46 +4090,64 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-13135800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>7780500</v>
+      </c>
+      <c r="F89" s="3">
+        <v>-8378900</v>
+      </c>
+      <c r="G89" s="3">
         <v>5263700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="H89" s="3">
         <v>-1641800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="I89" s="3">
         <v>1016900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="J89" s="3">
         <v>-8840000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="K89" s="3">
         <v>6709800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="L89" s="3">
         <v>-9819100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="M89" s="3">
         <v>11404300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="N89" s="3">
         <v>-285600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="O89" s="3">
         <v>-5473500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="P89" s="3">
         <v>877800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="Q89" s="3">
         <v>786800</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3505,46 +4162,58 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-34500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-79900</v>
+      </c>
+      <c r="G91" s="3">
         <v>-16700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="H91" s="3">
         <v>-15900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="I91" s="3">
         <v>-7200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="J91" s="3">
         <v>-61400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="K91" s="3">
         <v>-19100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="L91" s="3">
         <v>-10900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="M91" s="3">
         <v>-15100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="N91" s="3">
         <v>-41400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="O91" s="3">
         <v>-13000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="P91" s="3">
         <v>-25400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="Q91" s="3">
         <v>-17900</v>
       </c>
     </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3581,8 +4250,17 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3619,46 +4297,64 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>484400</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-830800</v>
+      </c>
+      <c r="F94" s="3">
+        <v>770000</v>
+      </c>
+      <c r="G94" s="3">
         <v>-1679400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="H94" s="3">
         <v>1981900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="I94" s="3">
         <v>-361600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="J94" s="3">
         <v>-99600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="K94" s="3">
         <v>-68200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="L94" s="3">
         <v>4463800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="M94" s="3">
         <v>-4887100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="N94" s="3">
         <v>1381000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="O94" s="3">
         <v>1399000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="P94" s="3">
         <v>956300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="Q94" s="3">
         <v>-2083600</v>
       </c>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3673,46 +4369,58 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3">
+        <v>205500</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3">
         <v>773900</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3">
         <v>238800</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K96" s="3">
         <v>928600</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M96" s="3">
         <v>182900</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O96" s="3">
         <v>793600</v>
       </c>
-      <c r="M96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q96" s="3">
         <v>211200</v>
       </c>
     </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3749,8 +4457,17 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3787,8 +4504,17 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3825,118 +4551,154 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1890900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>3557000</v>
+      </c>
+      <c r="F100" s="3">
+        <v>1588500</v>
+      </c>
+      <c r="G100" s="3">
         <v>3393600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="H100" s="3">
         <v>-504700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="I100" s="3">
         <v>-614400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="J100" s="3">
         <v>3939300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="K100" s="3">
         <v>-1712200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="L100" s="3">
         <v>-481800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="M100" s="3">
         <v>-681500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="N100" s="3">
         <v>2107300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="O100" s="3">
         <v>-1900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="P100" s="3">
         <v>944300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="Q100" s="3">
         <v>-690900</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F101" s="3">
+        <v>16400</v>
+      </c>
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="H101" s="3">
         <v>5300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="I101" s="3">
         <v>-2900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="J101" s="3">
         <v>-7800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="K101" s="3">
         <v>-1200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="L101" s="3">
         <v>35300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="M101" s="3">
         <v>-14100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="N101" s="3">
         <v>-12900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="O101" s="3">
         <v>97300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="P101" s="3">
         <v>16300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="Q101" s="3">
         <v>-7600</v>
       </c>
     </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-10760500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>10485600</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-6026000</v>
+      </c>
+      <c r="G102" s="3">
         <v>6975200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="H102" s="3">
         <v>-165400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="I102" s="3">
         <v>39500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="J102" s="3">
         <v>-4983900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="K102" s="3">
         <v>4929300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="L102" s="3">
         <v>-5831700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="M102" s="3">
         <v>5832700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="N102" s="3">
         <v>3194900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="O102" s="3">
         <v>-4077600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="P102" s="3">
         <v>2813600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="Q102" s="3">
         <v>-2001900</v>
       </c>
     </row>
